--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE3A1207-A11B-41EC-A3A2-41181E2FE1C1}"/>
+  <xr:revisionPtr revIDLastSave="503" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16838EC2-D865-465E-970D-560E459C0553}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="3" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="290">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -460,9 +460,6 @@
     <t>Escuela de Lenguaje Magrace</t>
   </si>
   <si>
-    <t>Escuela María Angélica Elizondo Briceño</t>
-  </si>
-  <si>
     <t>Escuela Santa Filomena</t>
   </si>
   <si>
@@ -541,9 +538,6 @@
     <t>Liceo Bicentenario María Mazzarello</t>
   </si>
   <si>
-    <t>Colegio Huillón</t>
-  </si>
-  <si>
     <t>Colegio Araucarias</t>
   </si>
   <si>
@@ -869,9 +863,6 @@
   </si>
   <si>
     <t>Colegio Genesaret</t>
-  </si>
-  <si>
-    <t>Escuela Jorge Alessandri Rodríguez</t>
   </si>
   <si>
     <t>PROCEDENCIA</t>
@@ -1625,10 +1616,10 @@
         <v>46</v>
       </c>
       <c r="D4">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4">
-        <v>1.109</v>
+        <v>1.1739999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1676,10 +1667,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7">
-        <v>1.0820000000000001</v>
+        <v>1.0489999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1693,10 +1684,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E8">
-        <v>1.0669999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1710,10 +1701,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>1.0189999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1727,10 +1718,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10">
-        <v>1.109</v>
+        <v>1.0940000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1744,10 +1735,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>1.08</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1761,10 +1752,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12">
-        <v>1.387</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1778,10 +1769,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>1.0860000000000001</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1795,10 +1786,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14">
-        <v>1.048</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1846,10 +1837,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17">
-        <v>1.044</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1897,10 +1888,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>1.012</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1931,10 +1922,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22">
-        <v>1.321</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1965,10 +1956,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E24">
-        <v>1.1539999999999999</v>
+        <v>1.169</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,10 +1973,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E25">
-        <v>1.0329999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,10 +2007,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E27">
-        <v>0.95399999999999996</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2033,10 +2024,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E28">
-        <v>1.05</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2050,10 +2041,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>1.0309999999999999</v>
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2067,10 +2058,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E30">
-        <v>0.99199999999999999</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2084,10 +2075,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E31">
-        <v>1.08</v>
+        <v>1.0720000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,10 +2092,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E32">
-        <v>1.0580000000000001</v>
+        <v>1.0609999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2135,10 +2126,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E34">
-        <v>0.95</v>
+        <v>0.94699999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,10 +2160,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E36">
-        <v>1.04</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,10 +2177,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E37">
-        <v>0.995</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2236,7 +2227,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C293"/>
+  <dimension ref="A1:C316"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2263,7 +2254,7 @@
         <v>46009</v>
       </c>
       <c r="C2" s="6">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2274,7 +2265,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2296,7 +2287,7 @@
         <v>46001</v>
       </c>
       <c r="C5" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2329,7 +2320,7 @@
         <v>46006</v>
       </c>
       <c r="C8" s="6">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2340,7 +2331,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2351,7 +2342,7 @@
         <v>46007</v>
       </c>
       <c r="C10" s="6">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2414,10 +2405,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>46083</v>
+        <v>46251</v>
       </c>
       <c r="C16" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2425,10 +2416,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>46162</v>
+        <v>46083</v>
       </c>
       <c r="C17" s="9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2436,10 +2427,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>46097</v>
+        <v>46162</v>
       </c>
       <c r="C18" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2447,10 +2438,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="8">
-        <v>46021</v>
+        <v>46097</v>
       </c>
       <c r="C19" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2458,10 +2449,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46080</v>
+        <v>46021</v>
       </c>
       <c r="C20" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2469,10 +2460,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="8">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C21" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2480,7 +2471,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="5">
-        <v>46022</v>
+        <v>46087</v>
       </c>
       <c r="C22" s="6">
         <v>3</v>
@@ -2491,7 +2482,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46161</v>
+        <v>46254</v>
       </c>
       <c r="C23" s="9">
         <v>1</v>
@@ -2502,7 +2493,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46086</v>
+        <v>46022</v>
       </c>
       <c r="C24" s="6">
         <v>3</v>
@@ -2513,10 +2504,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46211</v>
+        <v>46161</v>
       </c>
       <c r="C25" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2524,10 +2515,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46020</v>
+        <v>46086</v>
       </c>
       <c r="C26" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2535,10 +2526,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46076</v>
+        <v>46211</v>
       </c>
       <c r="C27" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2546,10 +2537,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46136</v>
+        <v>46020</v>
       </c>
       <c r="C28" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2557,10 +2548,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="C29" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2568,10 +2559,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46176</v>
+        <v>46136</v>
       </c>
       <c r="C30" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2579,10 +2570,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46182</v>
+        <v>46078</v>
       </c>
       <c r="C31" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2590,7 +2581,7 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46098</v>
+        <v>46176</v>
       </c>
       <c r="C32" s="6">
         <v>3</v>
@@ -2601,10 +2592,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C33" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2612,10 +2603,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C34" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2623,7 +2614,7 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46160</v>
+        <v>46098</v>
       </c>
       <c r="C35" s="9">
         <v>3</v>
@@ -2634,10 +2625,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="C36" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2645,10 +2636,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="C37" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2656,10 +2647,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46128</v>
+        <v>46160</v>
       </c>
       <c r="C38" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2667,10 +2658,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="C39" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2678,10 +2669,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46132</v>
+        <v>46099</v>
       </c>
       <c r="C40" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2689,10 +2680,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C41" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2700,10 +2691,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46225</v>
+        <v>46141</v>
       </c>
       <c r="C42" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2711,10 +2702,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46212</v>
+        <v>46132</v>
       </c>
       <c r="C43" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2722,10 +2713,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46210</v>
+        <v>46246</v>
       </c>
       <c r="C44" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2733,7 +2724,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C45" s="9">
         <v>2</v>
@@ -2744,10 +2735,10 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46104</v>
+        <v>46258</v>
       </c>
       <c r="C46" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2755,7 +2746,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46140</v>
+        <v>46225</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2766,10 +2757,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46106</v>
+        <v>46212</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2777,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46113</v>
+        <v>46091</v>
       </c>
       <c r="C49" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2788,7 +2779,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46184</v>
+        <v>46104</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -2799,10 +2790,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46090</v>
+        <v>46140</v>
       </c>
       <c r="C51" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2810,7 +2801,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46139</v>
+        <v>46106</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2821,7 +2812,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46148</v>
+        <v>46113</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2832,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46175</v>
+        <v>46184</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2843,10 +2834,10 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46125</v>
+        <v>46090</v>
       </c>
       <c r="C55" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2854,10 +2845,10 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="C56" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2865,10 +2856,10 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46177</v>
+        <v>46139</v>
       </c>
       <c r="C57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2876,7 +2867,7 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46156</v>
+        <v>46148</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
@@ -2887,7 +2878,7 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46213</v>
+        <v>46175</v>
       </c>
       <c r="C59" s="9">
         <v>1</v>
@@ -2898,7 +2889,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2909,7 +2900,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46226</v>
+        <v>46093</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2920,10 +2911,10 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46188</v>
+        <v>46177</v>
       </c>
       <c r="C62" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2931,7 +2922,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46101</v>
+        <v>46156</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2939,90 +2930,90 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46007</v>
+        <v>46245</v>
       </c>
       <c r="C64" s="6">
-        <v>77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46009</v>
+        <v>46213</v>
       </c>
       <c r="C65" s="9">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46000</v>
+        <v>46092</v>
       </c>
       <c r="C66" s="6">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46001</v>
+        <v>46226</v>
       </c>
       <c r="C67" s="9">
-        <v>82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46006</v>
+        <v>46238</v>
       </c>
       <c r="C68" s="6">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46010</v>
+        <v>46188</v>
       </c>
       <c r="C69" s="9">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46014</v>
+        <v>46101</v>
       </c>
       <c r="C70" s="6">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46002</v>
+        <v>46261</v>
       </c>
       <c r="C71" s="9">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3030,10 +3021,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C72" s="6">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3041,10 +3032,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="C73" s="9">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3052,10 +3043,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C74" s="6">
-        <v>30</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3063,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46022</v>
+        <v>46001</v>
       </c>
       <c r="C75" s="9">
-        <v>2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3074,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46080</v>
+        <v>46006</v>
       </c>
       <c r="C76" s="6">
-        <v>6</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3085,10 +3076,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46084</v>
+        <v>46010</v>
       </c>
       <c r="C77" s="9">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3096,10 +3087,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46125</v>
+        <v>46014</v>
       </c>
       <c r="C78" s="6">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3107,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46209</v>
+        <v>46002</v>
       </c>
       <c r="C79" s="9">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3118,10 +3109,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46091</v>
+        <v>46008</v>
       </c>
       <c r="C80" s="6">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3129,10 +3120,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46083</v>
+        <v>46003</v>
       </c>
       <c r="C81" s="9">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3140,10 +3131,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46105</v>
+        <v>46013</v>
       </c>
       <c r="C82" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3151,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46210</v>
+        <v>46262</v>
       </c>
       <c r="C83" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3162,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46211</v>
+        <v>46022</v>
       </c>
       <c r="C84" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3173,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46077</v>
+        <v>46080</v>
       </c>
       <c r="C85" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3184,10 +3175,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46118</v>
+        <v>46084</v>
       </c>
       <c r="C86" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3195,10 +3186,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46078</v>
+        <v>46125</v>
       </c>
       <c r="C87" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3206,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46217</v>
+        <v>46209</v>
       </c>
       <c r="C88" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3217,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46099</v>
+        <v>46091</v>
       </c>
       <c r="C89" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3228,10 +3219,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46104</v>
+        <v>46083</v>
       </c>
       <c r="C90" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3239,7 +3230,7 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46231</v>
+        <v>46105</v>
       </c>
       <c r="C91" s="9">
         <v>1</v>
@@ -3250,10 +3241,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46020</v>
+        <v>46210</v>
       </c>
       <c r="C92" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3261,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46076</v>
+        <v>46211</v>
       </c>
       <c r="C93" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3272,10 +3263,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46111</v>
+        <v>46077</v>
       </c>
       <c r="C94" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3283,10 +3274,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46087</v>
+        <v>46118</v>
       </c>
       <c r="C95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3294,10 +3285,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46140</v>
+        <v>46078</v>
       </c>
       <c r="C96" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3305,10 +3296,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46113</v>
+        <v>46217</v>
       </c>
       <c r="C97" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3316,10 +3307,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46119</v>
+        <v>46099</v>
       </c>
       <c r="C98" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3327,10 +3318,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46108</v>
+        <v>46104</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3338,10 +3329,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46098</v>
+        <v>46248</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3349,7 +3340,7 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46141</v>
+        <v>46231</v>
       </c>
       <c r="C101" s="9">
         <v>1</v>
@@ -3360,7 +3351,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46079</v>
+        <v>46258</v>
       </c>
       <c r="C102" s="6">
         <v>3</v>
@@ -3371,10 +3362,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46139</v>
+        <v>46020</v>
       </c>
       <c r="C103" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3382,10 +3373,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46148</v>
+        <v>46076</v>
       </c>
       <c r="C104" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3393,7 +3384,7 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46185</v>
+        <v>46111</v>
       </c>
       <c r="C105" s="9">
         <v>1</v>
@@ -3404,10 +3395,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46174</v>
+        <v>46087</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3415,10 +3406,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46092</v>
+        <v>46140</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3426,10 +3417,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46021</v>
+        <v>46113</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3437,10 +3428,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46177</v>
+        <v>46119</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3448,10 +3439,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46212</v>
+        <v>46108</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3459,10 +3450,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="C111" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3470,10 +3461,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46227</v>
+        <v>46141</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3481,10 +3472,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46188</v>
+        <v>46079</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3492,7 +3483,7 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46147</v>
+        <v>46139</v>
       </c>
       <c r="C114" s="6">
         <v>1</v>
@@ -3503,10 +3494,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46134</v>
+        <v>46148</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3514,7 +3505,7 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="C116" s="6">
         <v>1</v>
@@ -3525,7 +3516,7 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46190</v>
+        <v>46174</v>
       </c>
       <c r="C117" s="9">
         <v>1</v>
@@ -3536,7 +3527,7 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46225</v>
+        <v>46092</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -3544,109 +3535,109 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46003</v>
+        <v>46021</v>
       </c>
       <c r="C119" s="9">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46002</v>
+        <v>46177</v>
       </c>
       <c r="C120" s="6">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46008</v>
+        <v>46252</v>
       </c>
       <c r="C121" s="9">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46000</v>
+        <v>46212</v>
       </c>
       <c r="C122" s="6">
-        <v>96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46007</v>
+        <v>46086</v>
       </c>
       <c r="C123" s="9">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46001</v>
+        <v>46227</v>
       </c>
       <c r="C124" s="6">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46010</v>
+        <v>46188</v>
       </c>
       <c r="C125" s="9">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46006</v>
+        <v>46147</v>
       </c>
       <c r="C126" s="6">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46009</v>
+        <v>46134</v>
       </c>
       <c r="C127" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46015</v>
+        <v>46182</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3654,24 +3645,24 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46014</v>
+        <v>46190</v>
       </c>
       <c r="C129" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46013</v>
+        <v>46225</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3679,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46021</v>
+        <v>46003</v>
       </c>
       <c r="C131" s="9">
-        <v>2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3690,10 +3681,10 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46212</v>
+        <v>46002</v>
       </c>
       <c r="C132" s="6">
-        <v>2</v>
+        <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3701,10 +3692,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46077</v>
+        <v>46008</v>
       </c>
       <c r="C133" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3712,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46167</v>
+        <v>46000</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>96</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3723,10 +3714,10 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46209</v>
+        <v>46007</v>
       </c>
       <c r="C135" s="9">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3734,10 +3725,10 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46189</v>
+        <v>46001</v>
       </c>
       <c r="C136" s="6">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3745,10 +3736,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46170</v>
+        <v>46010</v>
       </c>
       <c r="C137" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3756,10 +3747,10 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46210</v>
+        <v>46006</v>
       </c>
       <c r="C138" s="6">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3767,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46093</v>
+        <v>46009</v>
       </c>
       <c r="C139" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3778,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46233</v>
+        <v>46014</v>
       </c>
       <c r="C140" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3789,10 +3780,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46090</v>
+        <v>46013</v>
       </c>
       <c r="C141" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3800,10 +3791,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C142" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3811,10 +3802,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46084</v>
+        <v>46212</v>
       </c>
       <c r="C143" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3822,10 +3813,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46134</v>
+        <v>46077</v>
       </c>
       <c r="C144" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3833,10 +3824,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46083</v>
+        <v>46167</v>
       </c>
       <c r="C145" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3844,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46022</v>
+        <v>46209</v>
       </c>
       <c r="C146" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3855,10 +3846,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46114</v>
+        <v>46189</v>
       </c>
       <c r="C147" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3866,7 +3857,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46135</v>
+        <v>46245</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -3877,10 +3868,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="C149" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3888,10 +3879,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46126</v>
+        <v>46210</v>
       </c>
       <c r="C150" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3899,10 +3890,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46120</v>
+        <v>46093</v>
       </c>
       <c r="C151" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3910,10 +3901,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46127</v>
+        <v>46233</v>
       </c>
       <c r="C152" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3921,10 +3912,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="C153" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3932,10 +3923,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46108</v>
+        <v>46078</v>
       </c>
       <c r="C154" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3943,10 +3934,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46020</v>
+        <v>46084</v>
       </c>
       <c r="C155" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3954,10 +3945,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46097</v>
+        <v>46134</v>
       </c>
       <c r="C156" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3965,10 +3956,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46177</v>
+        <v>46083</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3976,10 +3967,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46161</v>
+        <v>46262</v>
       </c>
       <c r="C158" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3987,7 +3978,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46129</v>
+        <v>46022</v>
       </c>
       <c r="C159" s="9">
         <v>1</v>
@@ -3998,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46080</v>
+        <v>46114</v>
       </c>
       <c r="C160" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4009,7 +4000,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46101</v>
+        <v>46135</v>
       </c>
       <c r="C161" s="9">
         <v>1</v>
@@ -4020,10 +4011,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="C162" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4031,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46150</v>
+        <v>46127</v>
       </c>
       <c r="C163" s="9">
         <v>1</v>
@@ -4042,7 +4033,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46141</v>
+        <v>46087</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -4053,7 +4044,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46085</v>
+        <v>46108</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4064,7 +4055,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C166" s="6">
         <v>1</v>
@@ -4075,10 +4066,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46118</v>
+        <v>46248</v>
       </c>
       <c r="C167" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4086,7 +4077,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46192</v>
+        <v>46252</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4097,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46079</v>
+        <v>46097</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4105,131 +4096,131 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46003</v>
+        <v>46177</v>
       </c>
       <c r="C170" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46000</v>
+        <v>46161</v>
       </c>
       <c r="C171" s="9">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46006</v>
+        <v>46129</v>
       </c>
       <c r="C172" s="6">
-        <v>171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46001</v>
+        <v>46080</v>
       </c>
       <c r="C173" s="9">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46014</v>
+        <v>46120</v>
       </c>
       <c r="C174" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46002</v>
+        <v>46101</v>
       </c>
       <c r="C175" s="9">
-        <v>171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46009</v>
+        <v>46155</v>
       </c>
       <c r="C176" s="6">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46010</v>
+        <v>46150</v>
       </c>
       <c r="C177" s="9">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46008</v>
+        <v>46141</v>
       </c>
       <c r="C178" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46007</v>
+        <v>46085</v>
       </c>
       <c r="C179" s="9">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46013</v>
+        <v>46148</v>
       </c>
       <c r="C180" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46080</v>
+        <v>46126</v>
       </c>
       <c r="C181" s="9">
         <v>2</v>
@@ -4237,10 +4228,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46209</v>
+        <v>46118</v>
       </c>
       <c r="C182" s="6">
         <v>2</v>
@@ -4248,10 +4239,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4259,24 +4250,24 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46090</v>
+        <v>46192</v>
       </c>
       <c r="C184" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46192</v>
+        <v>46079</v>
       </c>
       <c r="C185" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4284,10 +4275,10 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46079</v>
+        <v>46003</v>
       </c>
       <c r="C186" s="6">
-        <v>4</v>
+        <v>91</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4295,10 +4286,10 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46015</v>
+        <v>46000</v>
       </c>
       <c r="C187" s="9">
-        <v>1</v>
+        <v>132</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4306,10 +4297,10 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46085</v>
+        <v>46006</v>
       </c>
       <c r="C188" s="6">
-        <v>5</v>
+        <v>168</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4317,10 +4308,10 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46098</v>
+        <v>46001</v>
       </c>
       <c r="C189" s="9">
-        <v>2</v>
+        <v>173</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4328,10 +4319,10 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C190" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4339,10 +4330,10 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46078</v>
+        <v>46002</v>
       </c>
       <c r="C191" s="9">
-        <v>7</v>
+        <v>171</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4350,10 +4341,10 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46084</v>
+        <v>46009</v>
       </c>
       <c r="C192" s="6">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4361,10 +4352,10 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46128</v>
+        <v>46010</v>
       </c>
       <c r="C193" s="9">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4372,10 +4363,10 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46083</v>
+        <v>46008</v>
       </c>
       <c r="C194" s="6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4383,10 +4374,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46076</v>
+        <v>46007</v>
       </c>
       <c r="C195" s="9">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4394,10 +4385,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46099</v>
+        <v>46013</v>
       </c>
       <c r="C196" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4405,10 +4396,10 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46154</v>
+        <v>46258</v>
       </c>
       <c r="C197" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4416,10 +4407,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46226</v>
+        <v>46080</v>
       </c>
       <c r="C198" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4427,10 +4418,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46092</v>
+        <v>46209</v>
       </c>
       <c r="C199" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4438,7 +4429,7 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46022</v>
+        <v>46227</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4449,10 +4440,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46031</v>
+        <v>46090</v>
       </c>
       <c r="C201" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4460,10 +4451,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46120</v>
+        <v>46192</v>
       </c>
       <c r="C202" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4471,10 +4462,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C203" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4482,7 +4473,7 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46114</v>
+        <v>46015</v>
       </c>
       <c r="C204" s="6">
         <v>1</v>
@@ -4493,10 +4484,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46216</v>
+        <v>46085</v>
       </c>
       <c r="C205" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4504,10 +4495,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46037</v>
+        <v>46098</v>
       </c>
       <c r="C206" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4515,10 +4506,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C207" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4526,10 +4517,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46106</v>
+        <v>46078</v>
       </c>
       <c r="C208" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4537,10 +4528,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46211</v>
+        <v>46128</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4548,10 +4539,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46155</v>
+        <v>46083</v>
       </c>
       <c r="C210" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4559,7 +4550,7 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46210</v>
+        <v>46255</v>
       </c>
       <c r="C211" s="9">
         <v>2</v>
@@ -4570,10 +4561,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46112</v>
+        <v>46076</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4581,10 +4572,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46132</v>
+        <v>46084</v>
       </c>
       <c r="C213" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4592,10 +4583,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46108</v>
+        <v>46099</v>
       </c>
       <c r="C214" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4603,7 +4594,7 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="C215" s="9">
         <v>1</v>
@@ -4614,7 +4605,7 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46118</v>
+        <v>46226</v>
       </c>
       <c r="C216" s="6">
         <v>1</v>
@@ -4625,7 +4616,7 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46035</v>
+        <v>46092</v>
       </c>
       <c r="C217" s="9">
         <v>1</v>
@@ -4636,7 +4627,7 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46181</v>
+        <v>46022</v>
       </c>
       <c r="C218" s="6">
         <v>1</v>
@@ -4647,10 +4638,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46087</v>
+        <v>46031</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4658,7 +4649,7 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46030</v>
+        <v>46120</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
@@ -4669,10 +4660,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="C221" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4680,10 +4671,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46176</v>
+        <v>46077</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4691,7 +4682,7 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46101</v>
+        <v>46114</v>
       </c>
       <c r="C223" s="9">
         <v>1</v>
@@ -4702,10 +4693,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4713,7 +4704,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46142</v>
+        <v>46037</v>
       </c>
       <c r="C225" s="9">
         <v>1</v>
@@ -4721,164 +4712,164 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46001</v>
+        <v>46020</v>
       </c>
       <c r="C226" s="6">
-        <v>153</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46008</v>
+        <v>46106</v>
       </c>
       <c r="C227" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46003</v>
+        <v>46211</v>
       </c>
       <c r="C228" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46002</v>
+        <v>46239</v>
       </c>
       <c r="C229" s="9">
-        <v>111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46006</v>
+        <v>46155</v>
       </c>
       <c r="C230" s="6">
-        <v>145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46007</v>
+        <v>46210</v>
       </c>
       <c r="C231" s="9">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46000</v>
+        <v>46112</v>
       </c>
       <c r="C232" s="6">
-        <v>127</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46084</v>
+        <v>46132</v>
       </c>
       <c r="C233" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46013</v>
+        <v>46108</v>
       </c>
       <c r="C234" s="6">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46010</v>
+        <v>46148</v>
       </c>
       <c r="C235" s="9">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46021</v>
+        <v>46118</v>
       </c>
       <c r="C236" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46009</v>
+        <v>46035</v>
       </c>
       <c r="C237" s="9">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46083</v>
+        <v>46181</v>
       </c>
       <c r="C238" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46014</v>
+        <v>46087</v>
       </c>
       <c r="C239" s="9">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46157</v>
+        <v>46030</v>
       </c>
       <c r="C240" s="6">
         <v>2</v>
@@ -4886,21 +4877,21 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46079</v>
+        <v>46204</v>
       </c>
       <c r="C241" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46167</v>
+        <v>46176</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -4908,35 +4899,35 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46035</v>
+        <v>46101</v>
       </c>
       <c r="C243" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46085</v>
+        <v>46213</v>
       </c>
       <c r="C244" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46120</v>
+        <v>46142</v>
       </c>
       <c r="C245" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4944,10 +4935,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46114</v>
+        <v>46001</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>152</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4955,10 +4946,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46094</v>
+        <v>46008</v>
       </c>
       <c r="C247" s="9">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4966,10 +4957,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46192</v>
+        <v>46003</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4977,10 +4968,10 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46080</v>
+        <v>46002</v>
       </c>
       <c r="C249" s="9">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4988,10 +4979,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46127</v>
+        <v>46006</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>145</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4999,10 +4990,10 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
-        <v>46091</v>
+        <v>46007</v>
       </c>
       <c r="C251" s="9">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5010,10 +5001,10 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46090</v>
+        <v>46000</v>
       </c>
       <c r="C252" s="6">
-        <v>1</v>
+        <v>127</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5021,10 +5012,10 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46020</v>
+        <v>46084</v>
       </c>
       <c r="C253" s="9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5032,10 +5023,10 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
-        <v>46015</v>
+        <v>46013</v>
       </c>
       <c r="C254" s="6">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5043,10 +5034,10 @@
         <v>21</v>
       </c>
       <c r="B255" s="8">
-        <v>46217</v>
+        <v>46010</v>
       </c>
       <c r="C255" s="9">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5054,10 +5045,10 @@
         <v>21</v>
       </c>
       <c r="B256" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C256" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5065,10 +5056,10 @@
         <v>21</v>
       </c>
       <c r="B257" s="8">
-        <v>46209</v>
+        <v>46009</v>
       </c>
       <c r="C257" s="9">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5076,10 +5067,10 @@
         <v>21</v>
       </c>
       <c r="B258" s="5">
-        <v>46148</v>
+        <v>46083</v>
       </c>
       <c r="C258" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5087,10 +5078,10 @@
         <v>21</v>
       </c>
       <c r="B259" s="8">
-        <v>46105</v>
+        <v>46014</v>
       </c>
       <c r="C259" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5098,10 +5089,10 @@
         <v>21</v>
       </c>
       <c r="B260" s="5">
-        <v>46087</v>
+        <v>46157</v>
       </c>
       <c r="C260" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5109,7 +5100,7 @@
         <v>21</v>
       </c>
       <c r="B261" s="8">
-        <v>46107</v>
+        <v>46079</v>
       </c>
       <c r="C261" s="9">
         <v>3</v>
@@ -5120,10 +5111,10 @@
         <v>21</v>
       </c>
       <c r="B262" s="5">
-        <v>46086</v>
+        <v>46167</v>
       </c>
       <c r="C262" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5131,10 +5122,10 @@
         <v>21</v>
       </c>
       <c r="B263" s="8">
-        <v>46106</v>
+        <v>46035</v>
       </c>
       <c r="C263" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5142,7 +5133,7 @@
         <v>21</v>
       </c>
       <c r="B264" s="5">
-        <v>46150</v>
+        <v>46085</v>
       </c>
       <c r="C264" s="6">
         <v>3</v>
@@ -5153,10 +5144,10 @@
         <v>21</v>
       </c>
       <c r="B265" s="8">
-        <v>46104</v>
+        <v>46120</v>
       </c>
       <c r="C265" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5164,7 +5155,7 @@
         <v>21</v>
       </c>
       <c r="B266" s="5">
-        <v>46118</v>
+        <v>46114</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5175,10 +5166,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46231</v>
+        <v>46094</v>
       </c>
       <c r="C267" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5186,10 +5177,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46076</v>
+        <v>46192</v>
       </c>
       <c r="C268" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5197,10 +5188,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46182</v>
+        <v>46080</v>
       </c>
       <c r="C269" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5208,10 +5199,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46188</v>
+        <v>46127</v>
       </c>
       <c r="C270" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5219,10 +5210,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46154</v>
+        <v>46091</v>
       </c>
       <c r="C271" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5230,10 +5221,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46093</v>
+        <v>46090</v>
       </c>
       <c r="C272" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5241,10 +5232,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46122</v>
+        <v>46020</v>
       </c>
       <c r="C273" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5252,10 +5243,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46092</v>
+        <v>46015</v>
       </c>
       <c r="C274" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5263,10 +5254,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46156</v>
+        <v>46217</v>
       </c>
       <c r="C275" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5274,10 +5265,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46133</v>
+        <v>46078</v>
       </c>
       <c r="C276" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5285,10 +5276,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C277" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5296,7 +5287,7 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46210</v>
+        <v>46237</v>
       </c>
       <c r="C278" s="6">
         <v>1</v>
@@ -5307,10 +5298,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46232</v>
+        <v>46148</v>
       </c>
       <c r="C279" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5318,10 +5309,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46126</v>
+        <v>46105</v>
       </c>
       <c r="C280" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5329,10 +5320,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46022</v>
+        <v>46087</v>
       </c>
       <c r="C281" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5340,10 +5331,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C282" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5351,10 +5342,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46101</v>
+        <v>46086</v>
       </c>
       <c r="C283" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5362,10 +5353,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46097</v>
+        <v>46106</v>
       </c>
       <c r="C284" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5373,7 +5364,7 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46077</v>
+        <v>46150</v>
       </c>
       <c r="C285" s="9">
         <v>3</v>
@@ -5384,10 +5375,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46108</v>
+        <v>46104</v>
       </c>
       <c r="C286" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5395,7 +5386,7 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46233</v>
+        <v>46118</v>
       </c>
       <c r="C287" s="9">
         <v>1</v>
@@ -5406,10 +5397,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46098</v>
+        <v>46231</v>
       </c>
       <c r="C288" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5417,10 +5408,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46113</v>
+        <v>46076</v>
       </c>
       <c r="C289" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5428,7 +5419,7 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="C290" s="6">
         <v>1</v>
@@ -5439,7 +5430,7 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="C291" s="9">
         <v>1</v>
@@ -5450,7 +5441,7 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46031</v>
+        <v>46154</v>
       </c>
       <c r="C292" s="6">
         <v>1</v>
@@ -5461,9 +5452,262 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
+        <v>46093</v>
+      </c>
+      <c r="C293" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B294" s="5">
+        <v>46122</v>
+      </c>
+      <c r="C294" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" s="8">
+        <v>46092</v>
+      </c>
+      <c r="C295" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B296" s="5">
+        <v>46156</v>
+      </c>
+      <c r="C296" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C297" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B298" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C298" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B299" s="8">
+        <v>46210</v>
+      </c>
+      <c r="C299" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B300" s="5">
+        <v>46232</v>
+      </c>
+      <c r="C300" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B301" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C301" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B302" s="5">
+        <v>46022</v>
+      </c>
+      <c r="C302" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B303" s="8">
+        <v>46100</v>
+      </c>
+      <c r="C303" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B304" s="5">
+        <v>46101</v>
+      </c>
+      <c r="C304" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B305" s="8">
+        <v>46097</v>
+      </c>
+      <c r="C305" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B306" s="5">
+        <v>46077</v>
+      </c>
+      <c r="C306" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B307" s="8">
+        <v>46108</v>
+      </c>
+      <c r="C307" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B308" s="5">
+        <v>46233</v>
+      </c>
+      <c r="C308" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B309" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C309" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B310" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C310" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B311" s="8">
+        <v>46253</v>
+      </c>
+      <c r="C311" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B312" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C312" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B313" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C313" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B314" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C314" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B315" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C315" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B316" s="5">
         <v>46155</v>
       </c>
-      <c r="C293" s="9">
+      <c r="C316" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5550,7 +5794,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5595,13 +5839,13 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5612,13 +5856,13 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5629,7 +5873,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -5652,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5663,13 +5907,13 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5683,10 +5927,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5703,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5720,7 +5964,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5771,7 +6015,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5782,13 +6026,13 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5799,13 +6043,13 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5822,7 +6066,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5833,13 +6077,13 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5856,7 +6100,7 @@
         <v>25</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5884,7 +6128,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -5907,7 +6151,7 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5935,13 +6179,13 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5952,13 +6196,13 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28">
         <v>8</v>
       </c>
       <c r="E28">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5969,13 +6213,13 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5986,13 +6230,13 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D30">
         <v>7</v>
       </c>
       <c r="E30">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -6003,7 +6247,7 @@
         <v>7</v>
       </c>
       <c r="C31">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -6020,13 +6264,13 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D32">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E32">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6037,13 +6281,13 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6054,7 +6298,7 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -6071,13 +6315,13 @@
         <v>20</v>
       </c>
       <c r="C35">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6088,13 +6332,13 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D36">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6111,7 +6355,7 @@
         <v>13</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6122,13 +6366,13 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D38">
         <v>10</v>
       </c>
       <c r="E38">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6171,7 +6415,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6193,10 +6437,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -6204,7 +6448,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -6237,10 +6481,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -6248,7 +6492,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -6259,7 +6503,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6270,7 +6514,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -6281,7 +6525,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -6292,7 +6536,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6303,7 +6547,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6314,7 +6558,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -6325,7 +6569,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -6468,7 +6712,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -6534,7 +6778,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6567,7 +6811,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6600,10 +6844,10 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -6644,10 +6888,10 @@
         <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -6655,7 +6899,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6666,7 +6910,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -6677,7 +6921,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -6688,10 +6932,10 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -6699,7 +6943,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -6710,7 +6954,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -6721,7 +6965,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -6732,10 +6976,10 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -6743,7 +6987,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6754,7 +6998,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -6765,7 +7009,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -6776,7 +7020,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -6787,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -6798,7 +7042,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -6809,7 +7053,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -6820,7 +7064,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -6831,7 +7075,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -6842,7 +7086,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -6864,7 +7108,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -6875,7 +7119,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6886,7 +7130,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>189</v>
+        <v>51</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6897,7 +7141,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6908,7 +7152,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6919,7 +7163,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -6930,7 +7174,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6941,7 +7185,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6952,7 +7196,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6963,7 +7207,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6974,7 +7218,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6985,7 +7229,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6996,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7007,7 +7251,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7018,7 +7262,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7029,7 +7273,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7040,7 +7284,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7051,7 +7295,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7062,7 +7306,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -7073,7 +7317,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7084,7 +7328,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7095,7 +7339,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7106,7 +7350,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7117,7 +7361,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7128,7 +7372,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7139,7 +7383,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7150,7 +7394,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7161,7 +7405,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7172,7 +7416,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7183,7 +7427,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7194,7 +7438,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7205,7 +7449,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7216,7 +7460,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7227,7 +7471,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7238,7 +7482,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7249,7 +7493,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7257,13 +7501,13 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -7274,7 +7518,7 @@
         <v>116</v>
       </c>
       <c r="C101">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -7282,10 +7526,10 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -7293,10 +7537,10 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -7304,10 +7548,10 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -7315,7 +7559,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C105">
         <v>6</v>
@@ -7326,7 +7570,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C106">
         <v>6</v>
@@ -7337,10 +7581,10 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -7348,10 +7592,10 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -7370,7 +7614,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -7381,7 +7625,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -7392,7 +7636,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -7403,7 +7647,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -7414,7 +7658,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -7425,10 +7669,10 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -7436,7 +7680,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C116">
         <v>3</v>
@@ -7447,7 +7691,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -7458,10 +7702,10 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -7469,7 +7713,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -7480,7 +7724,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7491,7 +7735,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7502,7 +7746,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7513,7 +7757,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7524,7 +7768,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7535,7 +7779,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7546,7 +7790,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7557,7 +7801,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7568,7 +7812,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -7590,10 +7834,10 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -7601,7 +7845,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7612,7 +7856,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7623,7 +7867,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7634,7 +7878,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7645,7 +7889,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7656,7 +7900,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7667,7 +7911,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7678,7 +7922,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7689,7 +7933,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -7700,7 +7944,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7711,7 +7955,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7733,7 +7977,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7744,7 +7988,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -7755,7 +7999,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -7777,7 +8021,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -7799,7 +8043,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -7810,7 +8054,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -7821,7 +8065,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -7832,7 +8076,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7843,7 +8087,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -7854,7 +8098,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7865,7 +8109,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -7876,7 +8120,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7887,7 +8131,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -7898,7 +8142,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7909,7 +8153,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -7920,7 +8164,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -7931,7 +8175,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -7942,7 +8186,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7953,7 +8197,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7964,7 +8208,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -7975,7 +8219,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7986,7 +8230,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7997,7 +8241,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8008,7 +8252,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8019,7 +8263,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8030,7 +8274,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8041,7 +8285,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8052,7 +8296,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8063,7 +8307,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8074,7 +8318,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8085,7 +8329,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8096,7 +8340,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8107,7 +8351,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8118,7 +8362,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8129,7 +8373,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8140,7 +8384,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8151,7 +8395,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8173,7 +8417,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8184,7 +8428,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8192,13 +8436,13 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="C185">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -8206,10 +8450,10 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C186">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -8217,10 +8461,10 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C187">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8228,10 +8472,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C188">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8239,10 +8483,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="C189">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8253,7 +8497,7 @@
         <v>189</v>
       </c>
       <c r="C190">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8261,7 +8505,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="C191">
         <v>13</v>
@@ -8272,10 +8516,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="C192">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8283,10 +8527,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="C193">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8294,7 +8538,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -8305,10 +8549,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8316,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C196">
         <v>10</v>
@@ -8327,10 +8571,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8338,7 +8582,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C198">
         <v>9</v>
@@ -8349,10 +8593,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C199">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8360,10 +8604,10 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C200">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -8374,7 +8618,7 @@
         <v>192</v>
       </c>
       <c r="C201">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -8393,10 +8637,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8404,7 +8648,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>57</v>
+        <v>194</v>
       </c>
       <c r="C204">
         <v>6</v>
@@ -8415,7 +8659,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -8426,7 +8670,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8437,7 +8681,7 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -8470,7 +8714,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -8492,7 +8736,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8503,7 +8747,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8514,10 +8758,10 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C214">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -8525,7 +8769,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8536,7 +8780,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8547,7 +8791,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8558,7 +8802,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8569,7 +8813,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8580,7 +8824,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8591,7 +8835,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8602,7 +8846,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -8613,7 +8857,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -8624,10 +8868,10 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="C224">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -8635,7 +8879,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>64</v>
+        <v>199</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8646,7 +8890,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8657,7 +8901,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>203</v>
+        <v>64</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8668,7 +8912,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8679,7 +8923,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8690,7 +8934,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -8701,10 +8945,10 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -8712,7 +8956,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8723,7 +8967,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8745,7 +8989,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8756,7 +9000,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>220</v>
+        <v>159</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8767,7 +9011,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8778,7 +9022,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8789,7 +9033,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8800,7 +9044,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8811,7 +9055,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8822,7 +9066,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8833,7 +9077,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8844,7 +9088,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8855,7 +9099,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8866,7 +9110,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8877,7 +9121,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8888,7 +9132,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8899,7 +9143,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8910,7 +9154,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>217</v>
+        <v>123</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8921,7 +9165,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8932,7 +9176,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8943,7 +9187,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8954,7 +9198,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8965,7 +9209,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8976,7 +9220,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8987,7 +9231,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8998,7 +9242,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9009,7 +9253,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9020,7 +9264,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9031,7 +9275,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9042,7 +9286,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9053,7 +9297,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9064,7 +9308,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9075,7 +9319,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9086,7 +9330,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9097,7 +9341,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>116</v>
+        <v>219</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9108,7 +9352,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9119,7 +9363,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9130,7 +9374,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9141,7 +9385,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9174,7 +9418,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C274">
         <v>10</v>
@@ -9185,7 +9429,7 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="C275">
         <v>8</v>
@@ -9196,7 +9440,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="C276">
         <v>8</v>
@@ -9207,7 +9451,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C277">
         <v>6</v>
@@ -9229,7 +9473,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="C279">
         <v>5</v>
@@ -9240,7 +9484,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -9251,7 +9495,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9262,7 +9506,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9273,7 +9517,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9295,10 +9539,10 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="C285">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -9306,10 +9550,10 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="C286">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -9317,7 +9561,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>245</v>
+        <v>123</v>
       </c>
       <c r="C287">
         <v>3</v>
@@ -9328,7 +9572,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="C288">
         <v>3</v>
@@ -9350,7 +9594,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>243</v>
+        <v>124</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9361,7 +9605,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9372,7 +9616,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>241</v>
+        <v>100</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9383,7 +9627,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9394,7 +9638,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9405,7 +9649,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9416,7 +9660,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9427,7 +9671,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9438,7 +9682,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9449,10 +9693,10 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C299">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -9460,7 +9704,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -9471,7 +9715,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9482,7 +9726,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9493,7 +9737,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9504,7 +9748,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9515,7 +9759,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9526,7 +9770,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9537,7 +9781,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9548,7 +9792,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9559,7 +9803,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9570,7 +9814,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9581,7 +9825,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9592,7 +9836,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9603,7 +9847,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>70</v>
+        <v>241</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9614,7 +9858,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9625,7 +9869,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -9636,7 +9880,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>260</v>
+        <v>135</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -9647,7 +9891,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9658,7 +9902,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9669,7 +9913,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9680,7 +9924,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9691,7 +9935,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9713,7 +9957,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>169</v>
+        <v>260</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9724,7 +9968,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9735,7 +9979,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9746,7 +9990,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>258</v>
+        <v>179</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9757,7 +10001,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9768,7 +10012,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9779,7 +10023,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9790,7 +10034,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9812,7 +10056,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9834,7 +10078,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9845,7 +10089,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>63</v>
+        <v>255</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9856,7 +10100,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9867,7 +10111,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9878,7 +10122,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9889,7 +10133,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9900,7 +10144,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9911,7 +10155,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9922,7 +10166,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9933,7 +10177,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9944,7 +10188,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>91</v>
+        <v>250</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9955,7 +10199,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9966,7 +10210,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>171</v>
+        <v>253</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9977,7 +10221,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>268</v>
+        <v>161</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9988,7 +10232,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9999,33 +10243,17 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C349">
         <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B350" t="s">
-        <v>259</v>
-      </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
+      <c r="A350" s="12"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B351" t="s">
-        <v>265</v>
-      </c>
-      <c r="C351">
-        <v>1</v>
-      </c>
+      <c r="A351" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10062,7 +10290,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10073,7 +10301,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10084,7 +10312,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10095,7 +10323,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10106,7 +10334,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10117,7 +10345,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10128,7 +10356,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10139,7 +10367,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10150,7 +10378,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10161,7 +10389,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -10174,10 +10402,11 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -10185,10 +10414,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10196,10 +10425,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10207,10 +10436,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C3">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10218,10 +10447,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10229,7 +10458,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -10240,10 +10469,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10251,7 +10480,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10262,10 +10491,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C8">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10273,10 +10502,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C9">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10284,10 +10513,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10295,7 +10524,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -10306,21 +10535,21 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C12">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C13">
-        <v>885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -10328,10 +10557,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10339,10 +10568,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -10350,10 +10579,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C16">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -10361,10 +10590,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C17">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -10372,10 +10601,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -10383,10 +10612,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -10394,10 +10623,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -10405,10 +10634,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -10424,13 +10653,13 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -10441,7 +10670,7 @@
         <v>279</v>
       </c>
       <c r="C24">
-        <v>867</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -10449,10 +10678,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C25">
-        <v>25</v>
+        <v>868</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10460,10 +10689,10 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C26">
-        <v>114</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -10471,10 +10700,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C27">
-        <v>141</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -10482,10 +10711,10 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C28">
-        <v>79</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -10493,10 +10722,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -10504,10 +10733,10 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -10515,10 +10744,10 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -10526,21 +10755,21 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C33">
-        <v>708</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -10548,10 +10777,10 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>705</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -10559,10 +10788,10 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -10570,10 +10799,10 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C36">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -10581,10 +10810,10 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C37">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -10592,10 +10821,10 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C38">
-        <v>25</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -10603,10 +10832,10 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -10614,10 +10843,10 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -10625,10 +10854,10 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -10636,9 +10865,20 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C42">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43">
         <v>6</v>
       </c>
     </row>
@@ -10668,7 +10908,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10775,7 +11015,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -10885,7 +11125,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -10995,7 +11235,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="503" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16838EC2-D865-465E-970D-560E459C0553}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0269364-B8A4-4FB2-9C97-E4DB89EC4E33}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="3" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="290">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1047,10 +1047,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1582,10 +1578,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>1.3680000000000001</v>
+        <v>1.3160000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1684,10 +1680,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8">
-        <v>1.04</v>
+        <v>1.0269999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1735,10 +1731,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11">
-        <v>1.0569999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1803,10 +1799,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15">
-        <v>1.075</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1922,10 +1918,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22">
-        <v>1.357</v>
+        <v>1.393</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2024,10 +2020,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E28">
-        <v>1.036</v>
+        <v>1.0209999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2041,10 +2037,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>1.0549999999999999</v>
+        <v>1.0620000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2058,10 +2054,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E30">
-        <v>0.97499999999999998</v>
+        <v>0.98299999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2109,10 +2105,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.0429999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2126,10 +2122,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E34">
-        <v>0.94699999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2194,10 +2190,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E38">
-        <v>1.093</v>
+        <v>1.0880000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2227,7 +2223,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C316"/>
+  <dimension ref="A1:C322"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2265,7 +2261,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2331,7 +2327,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2342,7 +2338,7 @@
         <v>46007</v>
       </c>
       <c r="C10" s="6">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3068,7 +3064,7 @@
         <v>46006</v>
       </c>
       <c r="C76" s="6">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3329,10 +3325,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="C100" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3340,10 +3336,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C101" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3351,10 +3347,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C102" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3362,10 +3358,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C103" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3373,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C104" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3384,10 +3380,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C105" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3395,10 +3391,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C106" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3406,7 +3402,7 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C107" s="9">
         <v>2</v>
@@ -3417,10 +3413,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3428,10 +3424,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3439,10 +3435,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C111" s="9">
         <v>1</v>
@@ -3461,7 +3457,7 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C112" s="6">
         <v>1</v>
@@ -3472,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46079</v>
+        <v>46141</v>
       </c>
       <c r="C113" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3483,10 +3479,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3494,10 +3490,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3505,10 +3501,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3516,7 +3512,7 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C117" s="9">
         <v>1</v>
@@ -3527,7 +3523,7 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -3538,10 +3534,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C119" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3549,10 +3545,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3560,10 +3556,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3571,10 +3567,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C122" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3582,10 +3578,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46086</v>
+        <v>46212</v>
       </c>
       <c r="C123" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3593,10 +3589,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46227</v>
+        <v>46269</v>
       </c>
       <c r="C124" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3604,10 +3600,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46188</v>
+        <v>46086</v>
       </c>
       <c r="C125" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3615,10 +3611,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46147</v>
+        <v>46227</v>
       </c>
       <c r="C126" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3626,7 +3622,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3637,7 +3633,7 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3648,7 +3644,7 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3659,7 +3655,7 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3667,24 +3663,24 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C131" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C132" s="6">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3692,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C133" s="9">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3703,10 +3699,10 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C134" s="6">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3714,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C135" s="9">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3725,10 +3721,10 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C136" s="6">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3736,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C137" s="9">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3747,10 +3743,10 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C138" s="6">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3758,10 +3754,10 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C139" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3769,10 +3765,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C140" s="6">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,7 +3776,7 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C141" s="9">
         <v>2</v>
@@ -3791,10 +3787,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C142" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3802,7 +3798,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C143" s="9">
         <v>2</v>
@@ -3813,10 +3809,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C144" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3824,10 +3820,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C145" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3835,10 +3831,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C146" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3846,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C147" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3857,10 +3853,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C148" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3868,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C149" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3879,7 +3875,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C150" s="6">
         <v>1</v>
@@ -3890,7 +3886,7 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C151" s="9">
         <v>1</v>
@@ -3901,10 +3897,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C152" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3912,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C153" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3923,10 +3919,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C154" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3934,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C155" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3945,10 +3941,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C156" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3956,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C157" s="9">
         <v>4</v>
@@ -3967,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C158" s="6">
         <v>2</v>
@@ -3978,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3989,7 +3985,7 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C160" s="6">
         <v>2</v>
@@ -4000,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C161" s="9">
         <v>1</v>
@@ -4011,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46168</v>
+        <v>46114</v>
       </c>
       <c r="C162" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4022,7 +4018,7 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="C163" s="9">
         <v>1</v>
@@ -4033,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46087</v>
+        <v>46168</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4044,7 +4040,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4055,7 +4051,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46020</v>
+        <v>46087</v>
       </c>
       <c r="C166" s="6">
         <v>1</v>
@@ -4066,7 +4062,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46248</v>
+        <v>46108</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4077,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46252</v>
+        <v>46267</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4088,7 +4084,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4099,7 +4095,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46177</v>
+        <v>46248</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4110,10 +4106,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46161</v>
+        <v>46252</v>
       </c>
       <c r="C171" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4121,7 +4117,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4132,7 +4128,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46080</v>
+        <v>46177</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4143,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46120</v>
+        <v>46161</v>
       </c>
       <c r="C174" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4154,7 +4150,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4165,7 +4161,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46155</v>
+        <v>46080</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4176,7 +4172,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46150</v>
+        <v>46120</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4187,7 +4183,7 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46141</v>
+        <v>46101</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4198,7 +4194,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4209,7 +4205,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4220,10 +4216,10 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46126</v>
+        <v>46141</v>
       </c>
       <c r="C181" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4231,10 +4227,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46118</v>
+        <v>46085</v>
       </c>
       <c r="C182" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4242,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46258</v>
+        <v>46148</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4253,10 +4249,10 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46192</v>
+        <v>46126</v>
       </c>
       <c r="C184" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4264,43 +4260,43 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C185" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46003</v>
+        <v>46258</v>
       </c>
       <c r="C186" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46000</v>
+        <v>46192</v>
       </c>
       <c r="C187" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="C188" s="6">
-        <v>168</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4308,10 +4304,10 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C189" s="9">
-        <v>173</v>
+        <v>91</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4319,10 +4315,10 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C190" s="6">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4330,10 +4326,10 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C191" s="9">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4341,10 +4337,10 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C192" s="6">
-        <v>17</v>
+        <v>173</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4352,10 +4348,10 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C193" s="9">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4363,10 +4359,10 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C194" s="6">
-        <v>25</v>
+        <v>170</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4374,10 +4370,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C195" s="9">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4385,10 +4381,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C196" s="6">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4396,10 +4392,10 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46258</v>
+        <v>46008</v>
       </c>
       <c r="C197" s="9">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4407,10 +4403,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46080</v>
+        <v>46007</v>
       </c>
       <c r="C198" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4418,10 +4414,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46209</v>
+        <v>46013</v>
       </c>
       <c r="C199" s="9">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4429,10 +4425,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="C200" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4440,10 +4436,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C201" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4451,10 +4447,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46192</v>
+        <v>46209</v>
       </c>
       <c r="C202" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4462,10 +4458,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46079</v>
+        <v>46227</v>
       </c>
       <c r="C203" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4473,10 +4469,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C204" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4484,10 +4480,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46085</v>
+        <v>46192</v>
       </c>
       <c r="C205" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4495,10 +4491,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46098</v>
+        <v>46079</v>
       </c>
       <c r="C206" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4506,10 +4502,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C207" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4517,10 +4513,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C208" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4528,10 +4524,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46128</v>
+        <v>46098</v>
       </c>
       <c r="C209" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4539,10 +4535,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C210" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4550,10 +4546,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46255</v>
+        <v>46265</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4561,10 +4557,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="C212" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4572,10 +4568,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46084</v>
+        <v>46260</v>
       </c>
       <c r="C213" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4583,10 +4579,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46099</v>
+        <v>46128</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4594,10 +4590,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46154</v>
+        <v>46083</v>
       </c>
       <c r="C215" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4605,10 +4601,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46226</v>
+        <v>46255</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4616,10 +4612,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C217" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4627,7 +4623,7 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C218" s="6">
         <v>1</v>
@@ -4638,10 +4634,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46031</v>
+        <v>46084</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4649,7 +4645,7 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46120</v>
+        <v>46099</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
@@ -4660,10 +4656,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46237</v>
+        <v>46154</v>
       </c>
       <c r="C221" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4671,10 +4667,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46077</v>
+        <v>46226</v>
       </c>
       <c r="C222" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4682,7 +4678,7 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46114</v>
+        <v>46092</v>
       </c>
       <c r="C223" s="9">
         <v>1</v>
@@ -4693,10 +4689,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46216</v>
+        <v>46022</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4704,10 +4700,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4715,10 +4711,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46020</v>
+        <v>46120</v>
       </c>
       <c r="C226" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4726,10 +4722,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46106</v>
+        <v>46237</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4737,10 +4733,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46211</v>
+        <v>46077</v>
       </c>
       <c r="C228" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4748,7 +4744,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46239</v>
+        <v>46114</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4759,10 +4755,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46155</v>
+        <v>46216</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4770,10 +4766,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46210</v>
+        <v>46037</v>
       </c>
       <c r="C231" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4781,10 +4777,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4792,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4803,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46108</v>
+        <v>46211</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4814,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46148</v>
+        <v>46239</v>
       </c>
       <c r="C235" s="9">
         <v>1</v>
@@ -4825,7 +4821,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46118</v>
+        <v>46155</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4836,10 +4832,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46035</v>
+        <v>46210</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4847,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46181</v>
+        <v>46112</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4858,7 +4854,7 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46087</v>
+        <v>46132</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -4869,10 +4865,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46030</v>
+        <v>46108</v>
       </c>
       <c r="C240" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4880,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46204</v>
+        <v>46148</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -4891,7 +4887,7 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46176</v>
+        <v>46118</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -4902,7 +4898,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46101</v>
+        <v>46035</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4913,7 +4909,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46213</v>
+        <v>46181</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -4924,7 +4920,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46142</v>
+        <v>46087</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4932,68 +4928,68 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="C246" s="6">
-        <v>152</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46008</v>
+        <v>46204</v>
       </c>
       <c r="C247" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46003</v>
+        <v>46176</v>
       </c>
       <c r="C248" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46002</v>
+        <v>46101</v>
       </c>
       <c r="C249" s="9">
-        <v>109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46006</v>
+        <v>46213</v>
       </c>
       <c r="C250" s="6">
-        <v>145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46007</v>
+        <v>46142</v>
       </c>
       <c r="C251" s="9">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5001,10 +4997,10 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C252" s="6">
-        <v>127</v>
+        <v>151</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5012,10 +5008,10 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46084</v>
+        <v>46008</v>
       </c>
       <c r="C253" s="9">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5023,10 +5019,10 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C254" s="6">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5034,10 +5030,10 @@
         <v>21</v>
       </c>
       <c r="B255" s="8">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C255" s="9">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5045,10 +5041,10 @@
         <v>21</v>
       </c>
       <c r="B256" s="5">
-        <v>46021</v>
+        <v>46006</v>
       </c>
       <c r="C256" s="6">
-        <v>6</v>
+        <v>145</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5056,10 +5052,10 @@
         <v>21</v>
       </c>
       <c r="B257" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C257" s="9">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5067,10 +5063,10 @@
         <v>21</v>
       </c>
       <c r="B258" s="5">
-        <v>46083</v>
+        <v>46000</v>
       </c>
       <c r="C258" s="6">
-        <v>8</v>
+        <v>127</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5078,10 +5074,10 @@
         <v>21</v>
       </c>
       <c r="B259" s="8">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C259" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5089,10 +5085,10 @@
         <v>21</v>
       </c>
       <c r="B260" s="5">
-        <v>46157</v>
+        <v>46013</v>
       </c>
       <c r="C260" s="6">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5100,10 +5096,10 @@
         <v>21</v>
       </c>
       <c r="B261" s="8">
-        <v>46079</v>
+        <v>46010</v>
       </c>
       <c r="C261" s="9">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5111,10 +5107,10 @@
         <v>21</v>
       </c>
       <c r="B262" s="5">
-        <v>46167</v>
+        <v>46021</v>
       </c>
       <c r="C262" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5122,10 +5118,10 @@
         <v>21</v>
       </c>
       <c r="B263" s="8">
-        <v>46035</v>
+        <v>46009</v>
       </c>
       <c r="C263" s="9">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5133,10 +5129,10 @@
         <v>21</v>
       </c>
       <c r="B264" s="5">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="C264" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5144,10 +5140,10 @@
         <v>21</v>
       </c>
       <c r="B265" s="8">
-        <v>46120</v>
+        <v>46014</v>
       </c>
       <c r="C265" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5155,10 +5151,10 @@
         <v>21</v>
       </c>
       <c r="B266" s="5">
-        <v>46114</v>
+        <v>46157</v>
       </c>
       <c r="C266" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5166,7 +5162,7 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46094</v>
+        <v>46079</v>
       </c>
       <c r="C267" s="9">
         <v>3</v>
@@ -5177,7 +5173,7 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46192</v>
+        <v>46167</v>
       </c>
       <c r="C268" s="6">
         <v>1</v>
@@ -5188,10 +5184,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46080</v>
+        <v>46035</v>
       </c>
       <c r="C269" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5199,10 +5195,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46127</v>
+        <v>46085</v>
       </c>
       <c r="C270" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5210,7 +5206,7 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46091</v>
+        <v>46120</v>
       </c>
       <c r="C271" s="9">
         <v>2</v>
@@ -5221,7 +5217,7 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46090</v>
+        <v>46114</v>
       </c>
       <c r="C272" s="6">
         <v>1</v>
@@ -5232,10 +5228,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46020</v>
+        <v>46094</v>
       </c>
       <c r="C273" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5243,10 +5239,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46015</v>
+        <v>46192</v>
       </c>
       <c r="C274" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5254,10 +5250,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46217</v>
+        <v>46080</v>
       </c>
       <c r="C275" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5265,10 +5261,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="C276" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5276,10 +5272,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46209</v>
+        <v>46091</v>
       </c>
       <c r="C277" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5287,7 +5283,7 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46237</v>
+        <v>46090</v>
       </c>
       <c r="C278" s="6">
         <v>1</v>
@@ -5298,7 +5294,7 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C279" s="9">
         <v>2</v>
@@ -5309,10 +5305,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C280" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5320,10 +5316,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46087</v>
+        <v>46217</v>
       </c>
       <c r="C281" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5331,10 +5327,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46107</v>
+        <v>46078</v>
       </c>
       <c r="C282" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5342,10 +5338,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46086</v>
+        <v>46209</v>
       </c>
       <c r="C283" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5353,7 +5349,7 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46106</v>
+        <v>46237</v>
       </c>
       <c r="C284" s="6">
         <v>1</v>
@@ -5364,10 +5360,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="C285" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5375,10 +5371,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C286" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5386,10 +5382,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46118</v>
+        <v>46087</v>
       </c>
       <c r="C287" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5397,10 +5393,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46231</v>
+        <v>46107</v>
       </c>
       <c r="C288" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5408,10 +5404,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="C289" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5419,7 +5415,7 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46182</v>
+        <v>46106</v>
       </c>
       <c r="C290" s="6">
         <v>1</v>
@@ -5430,10 +5426,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46188</v>
+        <v>46150</v>
       </c>
       <c r="C291" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5441,10 +5437,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46154</v>
+        <v>46104</v>
       </c>
       <c r="C292" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5452,10 +5448,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C293" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5463,7 +5459,7 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46122</v>
+        <v>46231</v>
       </c>
       <c r="C294" s="6">
         <v>1</v>
@@ -5474,10 +5470,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C295" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5485,10 +5481,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="C296" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5496,7 +5492,7 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46133</v>
+        <v>46188</v>
       </c>
       <c r="C297" s="9">
         <v>1</v>
@@ -5507,7 +5503,7 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46189</v>
+        <v>46154</v>
       </c>
       <c r="C298" s="6">
         <v>1</v>
@@ -5518,10 +5514,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46210</v>
+        <v>46093</v>
       </c>
       <c r="C299" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5529,7 +5525,7 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46232</v>
+        <v>46122</v>
       </c>
       <c r="C300" s="6">
         <v>1</v>
@@ -5540,10 +5536,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="C301" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5551,10 +5547,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46022</v>
+        <v>46156</v>
       </c>
       <c r="C302" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5562,10 +5558,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="C303" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5573,7 +5569,7 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46101</v>
+        <v>46189</v>
       </c>
       <c r="C304" s="6">
         <v>1</v>
@@ -5584,10 +5580,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46097</v>
+        <v>46210</v>
       </c>
       <c r="C305" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5595,10 +5591,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46077</v>
+        <v>46232</v>
       </c>
       <c r="C306" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5606,7 +5602,7 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46108</v>
+        <v>46126</v>
       </c>
       <c r="C307" s="9">
         <v>1</v>
@@ -5617,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46233</v>
+        <v>46022</v>
       </c>
       <c r="C308" s="6">
         <v>1</v>
@@ -5628,7 +5624,7 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="C309" s="9">
         <v>2</v>
@@ -5639,7 +5635,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46113</v>
+        <v>46101</v>
       </c>
       <c r="C310" s="6">
         <v>1</v>
@@ -5650,10 +5646,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46253</v>
+        <v>46097</v>
       </c>
       <c r="C311" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5661,10 +5657,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46142</v>
+        <v>46077</v>
       </c>
       <c r="C312" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5672,7 +5668,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46244</v>
+        <v>46108</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5683,7 +5679,7 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46153</v>
+        <v>46233</v>
       </c>
       <c r="C314" s="6">
         <v>1</v>
@@ -5694,10 +5690,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="C315" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5705,9 +5701,75 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C316" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B317" s="8">
+        <v>46253</v>
+      </c>
+      <c r="C317" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B318" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C318" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B319" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C319" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B320" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C320" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B321" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C321" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B322" s="5">
         <v>46155</v>
       </c>
-      <c r="C316" s="6">
+      <c r="C322" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5760,7 +5822,7 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5862,7 +5924,7 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5913,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5981,7 +6043,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -6077,13 +6139,13 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -6100,7 +6162,7 @@
         <v>25</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -6196,7 +6258,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -6219,7 +6281,7 @@
         <v>3</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6230,7 +6292,7 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D30">
         <v>7</v>
@@ -6281,7 +6343,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -6298,7 +6360,7 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -6366,7 +6428,7 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -6866,10 +6928,10 @@
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -6888,10 +6950,10 @@
         <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -6899,7 +6961,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6910,7 +6972,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -6921,7 +6983,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -6932,7 +6994,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C48">
         <v>4</v>
@@ -6943,7 +7005,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -6954,7 +7016,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -6965,7 +7027,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -6976,7 +7038,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -6987,7 +7049,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6998,7 +7060,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -7009,7 +7071,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -7020,7 +7082,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -7031,7 +7093,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -7042,7 +7104,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -7053,7 +7115,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -7064,7 +7126,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -7075,7 +7137,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7086,7 +7148,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -7097,7 +7159,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -7108,7 +7170,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -7119,7 +7181,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7130,7 +7192,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7152,7 +7214,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7185,7 +7247,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7207,7 +7269,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7229,7 +7291,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7240,7 +7302,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7262,7 +7324,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7273,7 +7335,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7284,7 +7346,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7295,7 +7357,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7306,7 +7368,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -7328,7 +7390,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7350,7 +7412,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7372,7 +7434,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7394,7 +7456,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7471,7 +7533,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7482,7 +7544,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7493,7 +7555,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7504,7 +7566,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7540,7 +7602,7 @@
         <v>118</v>
       </c>
       <c r="C103">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -7713,7 +7775,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -7724,7 +7786,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7735,7 +7797,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7779,7 +7841,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7790,7 +7852,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7801,7 +7863,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7823,7 +7885,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -7834,7 +7896,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -7845,7 +7907,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7856,7 +7918,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7867,7 +7929,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7878,7 +7940,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7889,7 +7951,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7900,7 +7962,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7911,7 +7973,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7922,7 +7984,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7933,7 +7995,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -7944,7 +8006,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7955,7 +8017,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7966,7 +8028,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -7977,7 +8039,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7988,7 +8050,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -7999,7 +8061,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8010,7 +8072,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8021,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8032,7 +8094,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8043,7 +8105,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8054,7 +8116,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8065,7 +8127,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8076,7 +8138,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8087,7 +8149,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8098,7 +8160,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8109,7 +8171,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8120,7 +8182,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8131,7 +8193,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8142,7 +8204,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -8153,7 +8215,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8164,7 +8226,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8175,7 +8237,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8186,7 +8248,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8197,7 +8259,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>160</v>
+        <v>271</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8208,7 +8270,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8219,7 +8281,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8230,7 +8292,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8241,7 +8303,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8252,7 +8314,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8263,7 +8325,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8274,7 +8336,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8285,7 +8347,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8296,7 +8358,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8307,7 +8369,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8318,7 +8380,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8329,7 +8391,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8340,7 +8402,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8351,7 +8413,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8362,7 +8424,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8373,7 +8435,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8384,7 +8446,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8395,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8406,7 +8468,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>68</v>
+        <v>184</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8417,7 +8479,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8428,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8436,13 +8498,13 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="C185">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -8450,10 +8512,10 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C186">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -8461,10 +8523,10 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C187">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8472,10 +8534,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C188">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8483,10 +8545,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="C189">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8494,10 +8556,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C190">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8505,7 +8567,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="C191">
         <v>13</v>
@@ -8516,10 +8578,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C192">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8527,10 +8589,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="C193">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8538,7 +8600,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -8549,10 +8611,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C195">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8560,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C196">
         <v>10</v>
@@ -8571,10 +8633,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C197">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8582,7 +8644,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C198">
         <v>9</v>
@@ -8593,10 +8655,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="C199">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8604,7 +8666,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C200">
         <v>8</v>
@@ -8615,10 +8677,10 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="C201">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -8626,7 +8688,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="C202">
         <v>7</v>
@@ -8637,10 +8699,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C203">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8648,7 +8710,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="C204">
         <v>6</v>
@@ -8659,10 +8721,10 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>47</v>
+        <v>194</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -8670,7 +8732,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8681,7 +8743,7 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -8692,7 +8754,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -8703,7 +8765,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8714,10 +8776,10 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C210">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -8725,7 +8787,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8736,7 +8798,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8747,7 +8809,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8758,10 +8820,10 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C214">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -8769,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8780,7 +8842,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8791,7 +8853,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8802,7 +8864,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8813,7 +8875,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8824,7 +8886,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8835,7 +8897,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8846,7 +8908,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>289</v>
+        <v>59</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -8857,7 +8919,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -8868,10 +8930,10 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -8879,7 +8941,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8890,7 +8952,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8901,7 +8963,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>64</v>
+        <v>201</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8912,7 +8974,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8923,7 +8985,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8934,7 +8996,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -8945,10 +9007,10 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -8956,7 +9018,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8967,7 +9029,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8978,7 +9040,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8989,7 +9051,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9000,7 +9062,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9011,7 +9073,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9022,7 +9084,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9033,7 +9095,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9044,7 +9106,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9055,7 +9117,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9066,7 +9128,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9077,7 +9139,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9088,7 +9150,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9099,7 +9161,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9110,7 +9172,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9121,7 +9183,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9132,7 +9194,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9143,7 +9205,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9154,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9165,7 +9227,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9176,7 +9238,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9187,7 +9249,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9198,7 +9260,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9209,7 +9271,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9220,7 +9282,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9231,7 +9293,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9242,7 +9304,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9253,7 +9315,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9264,7 +9326,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9275,7 +9337,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9286,7 +9348,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9297,7 +9359,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9308,7 +9370,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9319,7 +9381,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9330,7 +9392,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9341,7 +9403,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9352,7 +9414,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9363,7 +9425,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9374,7 +9436,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9385,7 +9447,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>231</v>
+        <v>116</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9393,13 +9455,13 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>118</v>
+        <v>231</v>
       </c>
       <c r="C272">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -9407,10 +9469,10 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C273">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -9418,10 +9480,10 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="C274">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -9429,10 +9491,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="C275">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -9440,7 +9502,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>196</v>
+        <v>101</v>
       </c>
       <c r="C276">
         <v>8</v>
@@ -9451,10 +9513,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C277">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -9462,7 +9524,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="C278">
         <v>6</v>
@@ -9473,10 +9535,10 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C279">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -9484,7 +9546,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -9495,7 +9557,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>125</v>
+        <v>236</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9506,7 +9568,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9517,7 +9579,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9528,7 +9590,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9539,10 +9601,10 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C285">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -9550,7 +9612,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C286">
         <v>4</v>
@@ -9561,10 +9623,10 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C287">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -9572,7 +9634,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>242</v>
+        <v>123</v>
       </c>
       <c r="C288">
         <v>3</v>
@@ -9583,7 +9645,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9594,7 +9656,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9605,7 +9667,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>243</v>
+        <v>124</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9616,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9627,7 +9689,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9638,7 +9700,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9649,7 +9711,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9660,7 +9722,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9671,7 +9733,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9682,7 +9744,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9693,10 +9755,10 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C299">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -9704,7 +9766,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -9715,7 +9777,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9726,7 +9788,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9737,7 +9799,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9748,7 +9810,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9759,7 +9821,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9770,7 +9832,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9781,7 +9843,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9792,7 +9854,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>247</v>
+        <v>54</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9803,7 +9865,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9814,7 +9876,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9825,7 +9887,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9836,7 +9898,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9847,7 +9909,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>241</v>
+        <v>70</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9858,7 +9920,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9869,10 +9931,10 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="C315">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -9880,7 +9942,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>135</v>
+        <v>268</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -9891,7 +9953,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9902,7 +9964,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9913,7 +9975,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9924,7 +9986,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9935,7 +9997,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9946,7 +10008,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>134</v>
+        <v>259</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9957,7 +10019,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9968,7 +10030,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9979,7 +10041,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9990,7 +10052,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10001,7 +10063,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>249</v>
+        <v>179</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10012,7 +10074,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>144</v>
+        <v>249</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10023,7 +10085,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10034,7 +10096,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10045,7 +10107,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>49</v>
+        <v>206</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10056,7 +10118,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>269</v>
+        <v>49</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10067,7 +10129,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10078,7 +10140,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10089,7 +10151,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>255</v>
+        <v>116</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10100,7 +10162,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10111,7 +10173,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>251</v>
+        <v>91</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10122,7 +10184,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10133,7 +10195,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10144,7 +10206,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>63</v>
+        <v>266</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10155,7 +10217,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10166,7 +10228,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10177,7 +10239,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10188,7 +10250,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10199,7 +10261,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10210,7 +10272,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10221,7 +10283,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10232,7 +10294,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10243,14 +10305,22 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
+        <v>263</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B350" t="s">
         <v>264</v>
       </c>
-      <c r="C349">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" s="12"/>
+      <c r="C350">
+        <v>1</v>
+      </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="12"/>
@@ -10290,7 +10360,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10301,7 +10371,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10323,7 +10393,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10334,7 +10404,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10345,7 +10415,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10356,7 +10426,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10367,7 +10437,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10389,7 +10459,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -10428,7 +10498,7 @@
         <v>275</v>
       </c>
       <c r="C2">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10439,7 +10509,7 @@
         <v>276</v>
       </c>
       <c r="C3">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10450,7 +10520,7 @@
         <v>277</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10505,7 +10575,7 @@
         <v>276</v>
       </c>
       <c r="C9">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10527,7 +10597,7 @@
         <v>277</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -10560,7 +10630,7 @@
         <v>279</v>
       </c>
       <c r="C14">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10582,7 +10652,7 @@
         <v>276</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -10681,7 +10751,7 @@
         <v>276</v>
       </c>
       <c r="C25">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10703,7 +10773,7 @@
         <v>275</v>
       </c>
       <c r="C27">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -10714,7 +10784,7 @@
         <v>277</v>
       </c>
       <c r="C28">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -10780,7 +10850,7 @@
         <v>279</v>
       </c>
       <c r="C34">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
